--- a/dataset/construct/dataset_splits/data_size/2_percent/lmu/fold1.xlsx
+++ b/dataset/construct/dataset_splits/data_size/2_percent/lmu/fold1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>52872242</v>
+        <v>52028063</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,77 +625,79 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>86.7186858316222</v>
+        <v>79.7481177275838</v>
       </c>
       <c r="D2" t="n">
+        <v>27.7551020408163</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>33.984375</v>
-      </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>45</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>398</v>
+      </c>
+      <c r="I2" t="n">
+        <v>226</v>
+      </c>
       <c r="J2" t="n">
+        <v>159</v>
+      </c>
+      <c r="K2" t="n">
+        <v>783</v>
+      </c>
+      <c r="L2" t="n">
+        <v>398</v>
+      </c>
+      <c r="M2" t="n">
+        <v>74</v>
+      </c>
+      <c r="N2" t="n">
+        <v>95</v>
+      </c>
+      <c r="O2" t="n">
+        <v>567</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W2" t="n">
+        <v>26.96084735976707</v>
+      </c>
+      <c r="X2" t="n">
+        <v>25.19597660351653</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>295</v>
-      </c>
-      <c r="L2" t="n">
-        <v>191</v>
-      </c>
-      <c r="M2" t="n">
-        <v>140</v>
-      </c>
-      <c r="N2" t="n">
-        <v>626</v>
-      </c>
-      <c r="O2" t="n">
-        <v>295</v>
-      </c>
-      <c r="P2" t="n">
-        <v>191</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>113</v>
-      </c>
-      <c r="R2" t="n">
-        <v>599</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2</v>
-      </c>
-      <c r="X2" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>487.6</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -731,26 +718,17 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53688310</v>
+        <v>53687854</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -758,73 +736,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>92.7775496235455</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>89.5003422313484</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21.875</v>
+      </c>
       <c r="E3" t="n">
-        <v>30.4498269896194</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>43</v>
+      </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>299</v>
+      </c>
+      <c r="I3" t="n">
+        <v>589</v>
+      </c>
+      <c r="J3" t="n">
+        <v>356</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1244</v>
+      </c>
+      <c r="L3" t="n">
+        <v>201</v>
+      </c>
+      <c r="M3" t="n">
+        <v>219</v>
+      </c>
+      <c r="N3" t="n">
+        <v>324</v>
+      </c>
+      <c r="O3" t="n">
+        <v>744</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="W3" t="n">
+        <v>27.53380515489789</v>
+      </c>
+      <c r="X3" t="n">
+        <v>26.61396548311001</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>683</v>
-      </c>
-      <c r="L3" t="n">
-        <v>643</v>
-      </c>
-      <c r="M3" t="n">
-        <v>414</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1740</v>
-      </c>
-      <c r="O3" t="n">
-        <v>683</v>
-      </c>
-      <c r="P3" t="n">
-        <v>574</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>408</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1664</v>
-      </c>
-      <c r="S3" t="n">
-        <v>20</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>11</v>
-      </c>
-      <c r="V3" t="n">
-        <v>31</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>83.5</v>
-      </c>
       <c r="AA3" t="n">
-        <v>539.3</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -845,22 +829,17 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+        <v>137</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
